--- a/docs/data_inventory.xlsx
+++ b/docs/data_inventory.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uelac-my.sharepoint.com/personal/u3025339_uel_ac_uk/Documents/Desktop/wind_power_vws_uk/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="11_F25DC773A252ABDACC104852C95C4DDC5BDE58E0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56D9DD4E-9017-4583-9229-95E385FD2445}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="11_F25DC773A252ABDACC104852C95C4DDC5BDE58E0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{602061E3-591D-4E7F-B12F-58F43D5694A4}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="47">
   <si>
     <t>Dataset</t>
   </si>
@@ -124,6 +124,48 @@
   </si>
   <si>
     <t>raw</t>
+  </si>
+  <si>
+    <t>wind_generation_hourly</t>
+  </si>
+  <si>
+    <t>target variable dataset</t>
+  </si>
+  <si>
+    <t>wind_farm_elevation</t>
+  </si>
+  <si>
+    <t>wind farm dataset with elevation</t>
+  </si>
+  <si>
+    <t>wind_cornie</t>
+  </si>
+  <si>
+    <t>wind farm with vegetation</t>
+  </si>
+  <si>
+    <t>weather_feature</t>
+  </si>
+  <si>
+    <t>atmospheric variables</t>
+  </si>
+  <si>
+    <t>grid_capacity</t>
+  </si>
+  <si>
+    <t>wind farm with atmospheric variables</t>
+  </si>
+  <si>
+    <t>weighted_weather</t>
+  </si>
+  <si>
+    <t>weather_feature weighted</t>
+  </si>
+  <si>
+    <t>vws_dataset</t>
+  </si>
+  <si>
+    <t>weighted_weather with target variable</t>
   </si>
 </sst>
 </file>
@@ -454,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.33203125" customWidth="1"/>
@@ -611,6 +653,62 @@
         <v>28</v>
       </c>
     </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
